--- a/3.Problems for Revision.xlsx
+++ b/3.Problems for Revision.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="140">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -421,12 +421,6 @@
     <t xml:space="preserve">NOTE:  Check whether the problem requires a dummy node or not, check code for even and odd length Linked Lists, check what happens if head == null (empty list) and head.next == null (single node).</t>
   </si>
   <si>
-    <t xml:space="preserve">Pattern</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heaps</t>
-  </si>
-  <si>
     <t xml:space="preserve">2231. Largest Number After Digit Swaps by Parity</t>
   </si>
   <si>
@@ -434,6 +428,24 @@
   </si>
   <si>
     <t xml:space="preserve">Learn about java conversion methods: int → String → char[] and back to int</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find Median from Data Stream</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/find-median-from-data-stream/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice 2 heaps(max-min) to find median</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Number of the Smallest Unoccupied Chair</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/the-number-of-the-smallest-unoccupied-chair/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base problem - Many similar problems revolve around this pattern</t>
   </si>
 </sst>
 </file>
@@ -642,7 +654,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -747,12 +759,8 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
@@ -1208,8 +1216,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -1937,8 +1945,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2165,8 +2173,8 @@
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
@@ -2176,115 +2184,113 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:XFD15"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="8.34"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="11.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="64.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="19.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="69.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="10.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="41.57"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="8" style="26" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="27" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="64.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="19.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="69.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="10.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="68.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="50.08"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="16" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="26" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="16" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="28" t="s">
+    <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1" s="28" t="s">
+      <c r="B1" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="C1" s="27" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="27" t="s">
+        <v>3</v>
+      </c>
       <c r="E1" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="F1" s="29" t="s">
         <v>51</v>
       </c>
-      <c r="G1" s="29" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="33.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="16" t="n">
         <v>2231</v>
       </c>
       <c r="B2" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="E2" s="16" t="n">
+        <v>41</v>
+      </c>
+      <c r="F2" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="16" t="s">
+    </row>
+    <row r="3" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="16" t="n">
+        <v>295</v>
+      </c>
+      <c r="B3" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F2" s="16" t="n">
-        <v>41</v>
-      </c>
-      <c r="G2" s="16" t="s">
+      <c r="C3" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="16" t="s">
         <v>135</v>
       </c>
-    </row>
-    <row r="3" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD3" s="27"/>
-    </row>
-    <row r="4" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD4" s="27"/>
-    </row>
-    <row r="5" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD5" s="27"/>
-    </row>
-    <row r="6" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD6" s="27"/>
-    </row>
-    <row r="7" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD7" s="27"/>
-    </row>
-    <row r="8" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD8" s="27"/>
-    </row>
-    <row r="9" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD9" s="27"/>
-    </row>
-    <row r="10" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD10" s="27"/>
-    </row>
-    <row r="11" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD11" s="27"/>
-    </row>
-    <row r="12" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD12" s="27"/>
-    </row>
-    <row r="13" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD13" s="27"/>
-    </row>
-    <row r="14" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD14" s="27"/>
-    </row>
-    <row r="15" s="26" customFormat="true" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="XFD15" s="27"/>
+      <c r="E3" s="16" t="n">
+        <v>42</v>
+      </c>
+      <c r="F3" s="16" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="16" t="n">
+        <v>1942</v>
+      </c>
+      <c r="B4" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C4" s="16" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>43</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>139</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1" display="https://leetcode.com/problems/largest-number-after-digit-swaps-by-parity/"/>
+    <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/largest-number-after-digit-swaps-by-parity/"/>
+    <hyperlink ref="D3" r:id="rId2" display="https://leetcode.com/problems/find-median-from-data-stream/"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://leetcode.com/problems/the-number-of-the-smallest-unoccupied-chair/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
 </file>
--- a/3.Problems for Revision.xlsx
+++ b/3.Problems for Revision.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="143">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -446,6 +446,15 @@
   </si>
   <si>
     <t xml:space="preserve">Base problem - Many similar problems revolve around this pattern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meeting Rooms III</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/meeting-rooms-iii/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solve this and Leetcode 1942 together</t>
   </si>
 </sst>
 </file>
@@ -455,7 +464,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -572,6 +581,12 @@
       <family val="4"/>
       <charset val="1"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -654,7 +669,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -759,16 +774,20 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2184,7 +2203,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="8.34"/>
@@ -2195,27 +2214,27 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="68.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="50.08"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="16" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="26" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="20" width="11.53"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="16" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27" t="s">
+      <c r="B1" s="26" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="27" t="s">
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="27" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="27" t="s">
         <v>5</v>
       </c>
     </row>
@@ -2277,6 +2296,26 @@
       </c>
       <c r="F4" s="16" t="s">
         <v>139</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="16" t="n">
+        <v>2402</v>
+      </c>
+      <c r="B5" s="28" t="s">
+        <v>140</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>23</v>
+      </c>
+      <c r="D5" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>44</v>
+      </c>
+      <c r="F5" s="28" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
@@ -2284,6 +2323,7 @@
     <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/largest-number-after-digit-swaps-by-parity/"/>
     <hyperlink ref="D3" r:id="rId2" display="https://leetcode.com/problems/find-median-from-data-stream/"/>
     <hyperlink ref="D4" r:id="rId3" display="https://leetcode.com/problems/the-number-of-the-smallest-unoccupied-chair/"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://leetcode.com/problems/meeting-rooms-iii/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/3.Problems for Revision.xlsx
+++ b/3.Problems for Revision.xlsx
@@ -5,16 +5,17 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Practice Problems (Kunal + Anuj" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Two Pointers" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Fast&amp;Slow Pointers" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Sliding Window" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Intervals" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Linked List - In-Place Manipula" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="Heaps" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Binary Search" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Two Pointers" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Fast&amp;Slow Pointers" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Sliding Window" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Intervals" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Linked List - In-Place Manipula" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Heaps" sheetId="8" state="visible" r:id="rId10"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -26,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="165">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -91,7 +92,7 @@
     <t xml:space="preserve">https://youtu.be/9ByWqPzfXDU</t>
   </si>
   <si>
-    <t xml:space="preserve">Resursion</t>
+    <t xml:space="preserve">Recursion</t>
   </si>
   <si>
     <t xml:space="preserve">N-Queens</t>
@@ -106,7 +107,7 @@
     <t xml:space="preserve">https://youtu.be/nC1rbW2YSz0</t>
   </si>
   <si>
-    <t xml:space="preserve">Resursion + Backtracking</t>
+    <t xml:space="preserve">Recursion + Backtracking</t>
   </si>
   <si>
     <t xml:space="preserve">Sudoku Solver</t>
@@ -124,10 +125,76 @@
     <t xml:space="preserve">Similar to Leetcode 37</t>
   </si>
   <si>
+    <t xml:space="preserve">Find First and Last Position of Element in Sorted Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/W9QJ8HaRvJQ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Search</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Koko Eating Bananas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/koko-eating-bananas/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Search – Solve all 3 together</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Capacity To Ship Packages Within D Days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Split Array Largest Sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/split-array-largest-sum/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search in Rotated Sorted Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/search-in-rotated-sorted-array/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/5qGrJbHhqFs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Search – Solve both together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Search in Rotated Sorted Array II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/search-in-rotated-sorted-array-ii/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/w2G2W8l__pc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fair Distribution of Cookies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/fair-distribution-of-cookies/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Backtracking – Both Similar Questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find Minimum Time to Finish All Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/find-minimum-time-to-finish-all-jobs/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Split Array Largest Sum</t>
   </si>
   <si>
     <t xml:space="preserve">https://leetcode.com/problems/split-array-largest-sum/description/</t>
@@ -489,6 +556,13 @@
     </font>
     <font>
       <sz val="13"/>
+      <color theme="1"/>
+      <name val="Comic Sans MS"/>
+      <family val="4"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Comic Sans MS"/>
       <family val="4"/>
@@ -581,12 +655,6 @@
       <family val="4"/>
       <charset val="1"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Comic Sans MS"/>
-      <family val="4"/>
-    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -665,11 +733,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -678,47 +746,55 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -726,43 +802,47 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -774,20 +854,12 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1040,16 +1112,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15.85" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.78"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="67.91"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="69.28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="70.1"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.39"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="13.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="2" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1214,6 +1287,7 @@
         <v>31</v>
       </c>
     </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/pascals-triangle/"/>
@@ -1246,151 +1320,374 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:G17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="16.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.78"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="80.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="70.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>875</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F5" s="5"/>
+    </row>
+    <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>410</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="15.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>81</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="15.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>2305</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="1" t="n">
+        <v>1723</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="5"/>
+    </row>
+    <row r="14" s="6" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1"/>
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+    </row>
+    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="6"/>
+      <c r="B17" s="6"/>
+      <c r="C17" s="6"/>
+      <c r="D17" s="6"/>
+      <c r="E17" s="6"/>
+      <c r="F17" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="F4:F6"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="F11:F12"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://youtu.be/W9QJ8HaRvJQ"/>
+    <hyperlink ref="D4" r:id="rId3" display="https://leetcode.com/problems/koko-eating-bananas/"/>
+    <hyperlink ref="D5" r:id="rId4" display="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/"/>
+    <hyperlink ref="D6" r:id="rId5" display="https://leetcode.com/problems/split-array-largest-sum/"/>
+    <hyperlink ref="D8" r:id="rId6" display="https://leetcode.com/problems/search-in-rotated-sorted-array/"/>
+    <hyperlink ref="E8" r:id="rId7" display="https://youtu.be/5qGrJbHhqFs"/>
+    <hyperlink ref="D9" r:id="rId8" display="https://leetcode.com/problems/search-in-rotated-sorted-array-ii/"/>
+    <hyperlink ref="E9" r:id="rId9" display="https://youtu.be/w2G2W8l__pc"/>
+    <hyperlink ref="D11" r:id="rId10" display="https://leetcode.com/problems/fair-distribution-of-cookies/"/>
+    <hyperlink ref="D12" r:id="rId11" display="https://leetcode.com/problems/find-minimum-time-to-finish-all-jobs/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="129.5625" defaultRowHeight="19.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="6.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="69.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="85.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="129.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="5" width="129.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="69.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="85.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="129.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="7" width="129.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>32</v>
+      <c r="E1" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="7" t="n">
         <v>410</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="C2" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>35</v>
+      <c r="D2" s="10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="7" t="n">
         <v>1365</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C3" s="5" t="s">
+      <c r="B3" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>38</v>
+      <c r="D3" s="10" t="s">
+        <v>59</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="7" t="n">
         <v>246</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>41</v>
+      <c r="D4" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="7" t="n">
         <v>1650</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>41</v>
+      <c r="B5" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="7" t="n">
         <v>151</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>46</v>
+      <c r="B6" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="E6" s="10" t="s">
+        <v>68</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="7" t="n">
         <v>557</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7" s="5" t="s">
+      <c r="B7" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D7" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="E7" s="5" t="s">
-        <v>38</v>
+      <c r="D7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="7" t="n">
         <v>1886</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="B8" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>38</v>
+      <c r="D8" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>60</v>
       </c>
     </row>
   </sheetData>
@@ -1417,7 +1714,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1425,96 +1722,96 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="129.5625" defaultRowHeight="19.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="6.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="69.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="87.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="11.44"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="5" width="129.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="69.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="87.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="11.44"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="7" width="129.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>51</v>
+      <c r="E1" s="8" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="n">
+      <c r="A2" s="11" t="n">
         <v>142</v>
       </c>
-      <c r="B2" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="E2" s="5" t="n">
+      <c r="B2" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="7" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="9" t="n">
+      <c r="A3" s="11" t="n">
         <v>287</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>54</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="5" t="n">
+      <c r="B3" s="11" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="E3" s="7" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="7" t="n">
         <v>234</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C4" s="5" t="s">
+      <c r="B4" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="D4" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="7" t="n">
         <v>457</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="B5" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1529,7 +1826,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1537,208 +1834,208 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="19.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="5" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="5" width="63.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="5" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="5" width="67.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="5" width="13.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="5" width="43.9"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="5" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="63.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="67.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="43.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="7" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>60</v>
+      <c r="E1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="7" t="n">
         <v>209</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E2" s="5" t="n">
+      <c r="B2" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="E2" s="7" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="7" t="n">
         <v>2461</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="5" t="n">
+      <c r="B3" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E3" s="7" t="n">
         <v>13</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="5" t="n">
+      <c r="B4" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="E4" s="7" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="7" t="n">
         <v>187</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="B5" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="7" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="n">
+      <c r="A6" s="7" t="n">
         <v>904</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>70</v>
-      </c>
-      <c r="E6" s="5" t="n">
+      <c r="B6" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="7" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="n">
+      <c r="A7" s="7" t="n">
         <v>1838</v>
       </c>
-      <c r="B7" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="E7" s="5" t="n">
+      <c r="B7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E7" s="7" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>73</v>
+      <c r="F7" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="n">
+      <c r="A8" s="7" t="n">
         <v>424</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="E8" s="5" t="n">
+      <c r="B8" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E8" s="7" t="n">
         <v>18</v>
       </c>
-      <c r="F8" s="10" t="s">
-        <v>76</v>
+      <c r="F8" s="12" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="7" t="n">
         <v>1493</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>80</v>
+      <c r="B9" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="7" t="n">
         <v>1004</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>76</v>
+      <c r="B10" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="F10" s="12" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="2"/>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="11"/>
+      <c r="A11" s="13"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1755,7 +2052,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1763,190 +2060,190 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="35.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="68.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="59.26"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="12" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="35.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="68.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="59.26"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="15" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>60</v>
+      <c r="E1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="12" t="n">
+      <c r="A2" s="15" t="n">
         <v>56</v>
       </c>
-      <c r="B2" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D2" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E2" s="12" t="n">
+      <c r="B2" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="C2" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="15" t="n">
         <v>21</v>
       </c>
-      <c r="F2" s="12" t="s">
-        <v>86</v>
+      <c r="F2" s="15" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="n">
+      <c r="A3" s="15" t="n">
         <v>986</v>
       </c>
-      <c r="B3" s="12" t="s">
-        <v>87</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D3" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="E3" s="12" t="n">
+      <c r="B3" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>106</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="E3" s="15" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="16" t="n">
         <v>57</v>
       </c>
-      <c r="B4" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E4" s="14" t="n">
+      <c r="B4" s="17" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>112</v>
+      </c>
+      <c r="E4" s="17" t="n">
         <v>23</v>
       </c>
-      <c r="F4" s="13" t="s">
-        <v>91</v>
+      <c r="F4" s="16" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="n">
+      <c r="A5" s="15" t="n">
         <v>1288</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>92</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="12" t="s">
-        <v>93</v>
-      </c>
-      <c r="E5" s="12" t="n">
+      <c r="B5" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="E5" s="15" t="n">
         <v>24</v>
       </c>
-      <c r="F5" s="12" t="s">
-        <v>94</v>
+      <c r="F5" s="15" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="n">
+      <c r="A6" s="15" t="n">
         <v>731</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>95</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>96</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>97</v>
-      </c>
-      <c r="F6" s="12" t="s">
-        <v>98</v>
+      <c r="B6" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" s="15" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="n">
+      <c r="A7" s="15" t="n">
         <v>729</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="12" t="n">
+      <c r="B7" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>122</v>
+      </c>
+      <c r="E7" s="15" t="n">
         <v>27</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>98</v>
+      <c r="F7" s="15" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="n">
+      <c r="A8" s="15" t="n">
         <v>732</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="12" t="s">
+      <c r="B8" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="12" t="n">
+      <c r="D8" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="E8" s="15" t="n">
         <v>29</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>98</v>
+      <c r="F8" s="15" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="n">
+      <c r="A9" s="15" t="n">
         <v>352</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="E9" s="12" t="n">
+      <c r="D9" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="E9" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="12" t="s">
-        <v>105</v>
+      <c r="F9" s="15" t="s">
+        <v>127</v>
       </c>
     </row>
   </sheetData>
@@ -1970,7 +2267,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -1978,203 +2275,203 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="16.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="8.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="37.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="23.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="72.65"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="48.38"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="16" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="8.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="37.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="23.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="72.65"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="48.38"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="19" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>60</v>
+      <c r="E1" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="17" t="n">
+      <c r="A2" s="20" t="n">
         <v>206</v>
       </c>
-      <c r="B2" s="18" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="18" t="s">
+      <c r="B2" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C2" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="19" t="s">
-        <v>107</v>
-      </c>
-      <c r="E2" s="18" t="n">
+      <c r="D2" s="22" t="s">
+        <v>129</v>
+      </c>
+      <c r="E2" s="21" t="n">
         <v>32</v>
       </c>
-      <c r="F2" s="17" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" s="20"/>
+      <c r="F2" s="20" t="s">
+        <v>130</v>
+      </c>
+      <c r="G2" s="23"/>
     </row>
     <row r="3" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="n">
+      <c r="A3" s="20" t="n">
         <v>203</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>109</v>
-      </c>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="21" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="19" t="s">
-        <v>110</v>
-      </c>
-      <c r="E3" s="18" t="n">
+      <c r="D3" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="E3" s="21" t="n">
         <v>32</v>
       </c>
-      <c r="F3" s="17" t="s">
-        <v>111</v>
-      </c>
-      <c r="G3" s="20"/>
+      <c r="F3" s="20" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="23"/>
     </row>
     <row r="4" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="n">
+      <c r="A4" s="20" t="n">
         <v>92</v>
       </c>
-      <c r="B4" s="18" t="s">
-        <v>112</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>113</v>
-      </c>
-      <c r="E4" s="18" t="n">
+      <c r="B4" s="21" t="s">
+        <v>134</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="22" t="s">
+        <v>135</v>
+      </c>
+      <c r="E4" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>114</v>
-      </c>
-      <c r="G4" s="20"/>
+      <c r="F4" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="G4" s="23"/>
     </row>
     <row r="5" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="20" t="n">
         <v>143</v>
       </c>
-      <c r="B5" s="18" t="s">
-        <v>115</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>116</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="B5" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="E5" s="21" t="n">
         <v>33</v>
       </c>
-      <c r="F5" s="17" t="s">
-        <v>117</v>
-      </c>
-      <c r="G5" s="20"/>
+      <c r="F5" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="G5" s="23"/>
     </row>
     <row r="6" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="20" t="n">
         <v>328</v>
       </c>
-      <c r="B6" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="C6" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="19" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="B6" s="21" t="s">
+        <v>140</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="E6" s="21" t="n">
         <v>34</v>
       </c>
-      <c r="F6" s="17" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" s="21"/>
+      <c r="F6" s="20" t="s">
+        <v>142</v>
+      </c>
+      <c r="G6" s="24"/>
     </row>
     <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="n">
+      <c r="A7" s="20" t="n">
         <v>725</v>
       </c>
-      <c r="B7" s="18" t="s">
-        <v>121</v>
-      </c>
-      <c r="C7" s="18" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="19" t="s">
-        <v>122</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="B7" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="E7" s="21" t="n">
         <v>35</v>
       </c>
-      <c r="F7" s="17" t="s">
-        <v>123</v>
-      </c>
-      <c r="G7" s="21"/>
+      <c r="F7" s="20" t="s">
+        <v>145</v>
+      </c>
+      <c r="G7" s="24"/>
     </row>
     <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="19" t="n">
         <v>25</v>
       </c>
-      <c r="B8" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="C8" s="22" t="s">
+      <c r="B8" s="25" t="s">
+        <v>146</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="22" t="n">
+      <c r="D8" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="E8" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="F8" s="24"/>
-      <c r="G8" s="25"/>
+      <c r="F8" s="27"/>
+      <c r="G8" s="28"/>
     </row>
     <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="n">
+      <c r="A9" s="7" t="n">
         <v>2074</v>
       </c>
-      <c r="B9" s="22" t="s">
-        <v>126</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>127</v>
-      </c>
-      <c r="D9" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" s="22" t="n">
+      <c r="B9" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="E9" s="25" t="n">
         <v>37</v>
       </c>
-      <c r="F9" s="24" t="s">
-        <v>129</v>
+      <c r="F9" s="27" t="s">
+        <v>151</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="52.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="16" t="s">
-        <v>130</v>
+      <c r="D20" s="19" t="s">
+        <v>152</v>
       </c>
     </row>
   </sheetData>
@@ -2198,7 +2495,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -2206,116 +2503,116 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="16" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="16" width="64.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="16" width="19.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="16" width="69.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="16" width="10.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="16" width="68.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="16" width="50.08"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="16" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="20" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="16" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="64.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="19.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="69.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="10.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="68.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="19" width="50.08"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="19" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="23" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="19" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
+      <c r="B1" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="26" t="s">
+      <c r="C1" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
-        <v>51</v>
-      </c>
-      <c r="F1" s="27" t="s">
+      <c r="E1" s="30" t="s">
+        <v>73</v>
+      </c>
+      <c r="F1" s="30" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="n">
+      <c r="A2" s="19" t="n">
         <v>2231</v>
       </c>
-      <c r="B2" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="19" t="s">
+        <v>153</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="E2" s="16" t="n">
+      <c r="D2" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E2" s="19" t="n">
         <v>41</v>
       </c>
-      <c r="F2" s="16" t="s">
-        <v>133</v>
+      <c r="F2" s="19" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="16" t="n">
+      <c r="A3" s="19" t="n">
         <v>295</v>
       </c>
-      <c r="B3" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="C3" s="16" t="s">
+      <c r="B3" s="19" t="s">
+        <v>156</v>
+      </c>
+      <c r="C3" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D3" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="16" t="n">
+      <c r="D3" s="19" t="s">
+        <v>157</v>
+      </c>
+      <c r="E3" s="19" t="n">
         <v>42</v>
       </c>
-      <c r="F3" s="16" t="s">
-        <v>136</v>
+      <c r="F3" s="19" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="19" t="n">
         <v>1942</v>
       </c>
-      <c r="B4" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C4" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E4" s="16" t="n">
+      <c r="B4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="E4" s="19" t="n">
         <v>43</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>139</v>
+      <c r="F4" s="19" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="19" t="n">
         <v>2402</v>
       </c>
-      <c r="B5" s="28" t="s">
-        <v>140</v>
-      </c>
-      <c r="C5" s="16" t="s">
+      <c r="B5" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="E5" s="16" t="n">
+      <c r="D5" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="E5" s="19" t="n">
         <v>44</v>
       </c>
-      <c r="F5" s="28" t="s">
-        <v>142</v>
+      <c r="F5" s="19" t="s">
+        <v>164</v>
       </c>
     </row>
   </sheetData>

--- a/3.Problems for Revision.xlsx
+++ b/3.Problems for Revision.xlsx
@@ -143,7 +143,7 @@
     <t xml:space="preserve">https://leetcode.com/problems/koko-eating-bananas/</t>
   </si>
   <si>
-    <t xml:space="preserve">Binary Search – Solve all 3 together</t>
+    <t xml:space="preserve">Binary Search on Answers – Solve all 3 together</t>
   </si>
   <si>
     <t xml:space="preserve"> Capacity To Ship Packages Within D Days</t>
@@ -762,7 +762,7 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1328,7 +1328,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="80.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="70.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.39"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36.87"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.54"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
   </cols>

--- a/3.Problems for Revision.xlsx
+++ b/3.Problems for Revision.xlsx
@@ -5,10 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
   </bookViews>
   <sheets>
-    <sheet name="Practice Problems (Kunal + Anuj" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="Practice Problems (Striver + Ku" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Binary Search" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="Two Pointers" sheetId="3" state="visible" r:id="rId5"/>
     <sheet name="Fast&amp;Slow Pointers" sheetId="4" state="visible" r:id="rId6"/>
@@ -16,6 +16,8 @@
     <sheet name="Intervals" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Linked List - In-Place Manipula" sheetId="7" state="visible" r:id="rId9"/>
     <sheet name="Heaps" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Trees" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="Sheet10" sheetId="10" state="visible" r:id="rId12"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="187">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -143,7 +145,19 @@
     <t xml:space="preserve">https://leetcode.com/problems/koko-eating-bananas/</t>
   </si>
   <si>
-    <t xml:space="preserve">Binary Search on Answers – Solve all 3 together</t>
+    <t xml:space="preserve">https://youtu.be/qyfekrNni90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Search on Answers – Solve all 4 together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum Number of Days to Make m Bouquets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/minimum-number-of-days-to-make-m-bouquets/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/TXAuxeYBTdg</t>
   </si>
   <si>
     <t xml:space="preserve"> Capacity To Ship Packages Within D Days</t>
@@ -152,6 +166,9 @@
     <t xml:space="preserve">https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/</t>
   </si>
   <si>
+    <t xml:space="preserve">https://youtu.be/MG-Ac4TAvTY</t>
+  </si>
+  <si>
     <t xml:space="preserve">Split Array Largest Sum</t>
   </si>
   <si>
@@ -522,6 +539,57 @@
   </si>
   <si>
     <t xml:space="preserve">Solve this and Leetcode 1942 together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum Depth of Binary Tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/maximum-depth-of-binary-tree/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/eD3tmO66aBA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Solve Both Together</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Balanced Binary Tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/balanced-binary-tree/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Yt50Jfbd8Po</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diameter of Binary Tree</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/diameter-of-binary-tree/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/Rezetez59Nk</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Tree Maximum Path Sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/binary-tree-maximum-path-sum/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://youtu.be/WszrfSwMz58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Binary Tree Tilt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/binary-tree-tilt/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Longest Univalue Path</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/longest-univalue-path/</t>
   </si>
 </sst>
 </file>
@@ -737,7 +805,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="34">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -860,6 +928,18 @@
     </xf>
     <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1315,12 +1395,102 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="64.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="19.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="69.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="51.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="68.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="19" width="50.08"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="19" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="23" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="13"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="13"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="13"/>
+      <c r="F5" s="13"/>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="13"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="16.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.78"/>
@@ -1328,7 +1498,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.36"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="80.55"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="70.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="36.88"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.54"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
   </cols>
@@ -1386,147 +1556,177 @@
       <c r="D4" s="1" t="s">
         <v>37</v>
       </c>
+      <c r="E4" s="1" t="s">
+        <v>38</v>
+      </c>
       <c r="F4" s="5" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
-        <v>1011</v>
+        <v>1482</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="F5" s="5"/>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
+        <v>1011</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="F6" s="5"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>410</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B7" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F6" s="5"/>
-    </row>
-    <row r="7" customFormat="false" ht="15.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
+      <c r="D7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="F7" s="5"/>
+    </row>
+    <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F8" s="5"/>
+    </row>
+    <row r="10" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>33</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="B10" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>81</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="F9" s="5"/>
-    </row>
-    <row r="10" customFormat="false" ht="15.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
+      <c r="B11" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="5"/>
+    </row>
+    <row r="12" customFormat="false" ht="15.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="13" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="1" t="n">
         <v>2305</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
+      <c r="B13" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="n">
         <v>1723</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B14" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="5"/>
-    </row>
-    <row r="14" s="6" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="17" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="6"/>
-      <c r="B17" s="6"/>
-      <c r="C17" s="6"/>
-      <c r="D17" s="6"/>
-      <c r="E17" s="6"/>
-      <c r="F17" s="6"/>
+      <c r="D14" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="5"/>
+    </row>
+    <row r="16" s="6" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="1"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+    </row>
+    <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6"/>
+      <c r="B19" s="6"/>
+      <c r="C19" s="6"/>
+      <c r="D19" s="6"/>
+      <c r="E19" s="6"/>
+      <c r="F19" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="F4:F6"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="F10:F11"/>
+    <mergeCell ref="F13:F14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/find-first-and-last-position-of-element-in-sorted-array/"/>
     <hyperlink ref="E2" r:id="rId2" display="https://youtu.be/W9QJ8HaRvJQ"/>
     <hyperlink ref="D4" r:id="rId3" display="https://leetcode.com/problems/koko-eating-bananas/"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://leetcode.com/problems/split-array-largest-sum/"/>
-    <hyperlink ref="D8" r:id="rId6" display="https://leetcode.com/problems/search-in-rotated-sorted-array/"/>
-    <hyperlink ref="E8" r:id="rId7" display="https://youtu.be/5qGrJbHhqFs"/>
-    <hyperlink ref="D9" r:id="rId8" display="https://leetcode.com/problems/search-in-rotated-sorted-array-ii/"/>
-    <hyperlink ref="E9" r:id="rId9" display="https://youtu.be/w2G2W8l__pc"/>
-    <hyperlink ref="D11" r:id="rId10" display="https://leetcode.com/problems/fair-distribution-of-cookies/"/>
-    <hyperlink ref="D12" r:id="rId11" display="https://leetcode.com/problems/find-minimum-time-to-finish-all-jobs/"/>
+    <hyperlink ref="E4" r:id="rId4" display="https://youtu.be/qyfekrNni90"/>
+    <hyperlink ref="D5" r:id="rId5" display="https://leetcode.com/problems/minimum-number-of-days-to-make-m-bouquets/"/>
+    <hyperlink ref="E5" r:id="rId6" display="https://youtu.be/TXAuxeYBTdg"/>
+    <hyperlink ref="D6" r:id="rId7" display="https://leetcode.com/problems/capacity-to-ship-packages-within-d-days/"/>
+    <hyperlink ref="E6" r:id="rId8" display="https://youtu.be/MG-Ac4TAvTY"/>
+    <hyperlink ref="D7" r:id="rId9" display="https://leetcode.com/problems/split-array-largest-sum/"/>
+    <hyperlink ref="D10" r:id="rId10" display="https://leetcode.com/problems/search-in-rotated-sorted-array/"/>
+    <hyperlink ref="E10" r:id="rId11" display="https://youtu.be/5qGrJbHhqFs"/>
+    <hyperlink ref="D11" r:id="rId12" display="https://leetcode.com/problems/search-in-rotated-sorted-array-ii/"/>
+    <hyperlink ref="E11" r:id="rId13" display="https://youtu.be/w2G2W8l__pc"/>
+    <hyperlink ref="D13" r:id="rId14" display="https://leetcode.com/problems/fair-distribution-of-cookies/"/>
+    <hyperlink ref="D14" r:id="rId15" display="https://leetcode.com/problems/find-minimum-time-to-finish-all-jobs/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1568,7 +1768,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1576,16 +1776,16 @@
         <v>410</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="C2" s="9" t="s">
         <v>23</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="E2" s="10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1593,16 +1793,16 @@
         <v>1365</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1610,16 +1810,16 @@
         <v>246</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1627,16 +1827,16 @@
         <v>1650</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1644,16 +1844,16 @@
         <v>151</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1661,16 +1861,16 @@
         <v>557</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1678,16 +1878,16 @@
         <v>1886</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
@@ -1744,7 +1944,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1752,13 +1952,13 @@
         <v>142</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="C2" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>8</v>
@@ -1769,13 +1969,13 @@
         <v>287</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="C3" s="11" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>9</v>
@@ -1786,13 +1986,13 @@
         <v>234</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>9</v>
@@ -1803,13 +2003,13 @@
         <v>457</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>11</v>
@@ -1857,10 +2057,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1868,13 +2068,13 @@
         <v>209</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="E2" s="7" t="n">
         <v>13</v>
@@ -1885,13 +2085,13 @@
         <v>2461</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="E3" s="7" t="n">
         <v>13</v>
@@ -1902,13 +2102,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="E4" s="7" t="n">
         <v>14</v>
@@ -1919,13 +2119,13 @@
         <v>187</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="C5" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="E5" s="7" t="n">
         <v>15</v>
@@ -1936,13 +2136,13 @@
         <v>904</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="C6" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="E6" s="7" t="n">
         <v>16</v>
@@ -1953,19 +2153,19 @@
         <v>1838</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="C7" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
       <c r="E7" s="7" t="n">
         <v>17</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1973,19 +2173,19 @@
         <v>424</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="C8" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>97</v>
+        <v>102</v>
       </c>
       <c r="E8" s="7" t="n">
         <v>18</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>98</v>
+        <v>103</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1993,19 +2193,19 @@
         <v>1493</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>99</v>
+        <v>104</v>
       </c>
       <c r="C9" s="7" t="s">
         <v>13</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2013,19 +2213,19 @@
         <v>1004</v>
       </c>
       <c r="B10" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F10" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2083,10 +2283,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2094,19 +2294,19 @@
         <v>56</v>
       </c>
       <c r="B2" s="15" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="C2" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D2" s="15" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="E2" s="15" t="n">
         <v>21</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2114,13 +2314,13 @@
         <v>986</v>
       </c>
       <c r="B3" s="15" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="C3" s="15" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="D3" s="15" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E3" s="15" t="n">
         <v>22</v>
@@ -2131,19 +2331,19 @@
         <v>57</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="C4" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E4" s="17" t="n">
         <v>23</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2151,19 +2351,19 @@
         <v>1288</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="C5" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E5" s="15" t="n">
         <v>24</v>
       </c>
       <c r="F5" s="15" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2171,19 +2371,19 @@
         <v>731</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E6" s="15" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="F6" s="15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2191,19 +2391,19 @@
         <v>729</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="C7" s="15" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>27</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2211,19 +2411,19 @@
         <v>732</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="C8" s="15" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="E8" s="15" t="n">
         <v>29</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>120</v>
+        <v>125</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2231,19 +2431,19 @@
         <v>352</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="C9" s="15" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>126</v>
+        <v>131</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>30</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>127</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -2298,10 +2498,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>82</v>
+        <v>87</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2309,19 +2509,19 @@
         <v>206</v>
       </c>
       <c r="B2" s="21" t="s">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="C2" s="21" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="22" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="E2" s="21" t="n">
         <v>32</v>
       </c>
       <c r="F2" s="20" t="s">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="G2" s="23"/>
     </row>
@@ -2330,19 +2530,19 @@
         <v>203</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>7</v>
       </c>
       <c r="D3" s="22" t="s">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="E3" s="21" t="n">
         <v>32</v>
       </c>
       <c r="F3" s="20" t="s">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="G3" s="23"/>
     </row>
@@ -2351,19 +2551,19 @@
         <v>92</v>
       </c>
       <c r="B4" s="21" t="s">
-        <v>134</v>
+        <v>139</v>
       </c>
       <c r="C4" s="21" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="22" t="s">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="E4" s="21" t="n">
         <v>33</v>
       </c>
       <c r="F4" s="20" t="s">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G4" s="23"/>
     </row>
@@ -2372,19 +2572,19 @@
         <v>143</v>
       </c>
       <c r="B5" s="21" t="s">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="C5" s="21" t="s">
         <v>13</v>
       </c>
       <c r="D5" s="22" t="s">
-        <v>138</v>
+        <v>143</v>
       </c>
       <c r="E5" s="21" t="n">
         <v>33</v>
       </c>
       <c r="F5" s="20" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="G5" s="23"/>
     </row>
@@ -2393,19 +2593,19 @@
         <v>328</v>
       </c>
       <c r="B6" s="21" t="s">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="C6" s="21" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="22" t="s">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>34</v>
       </c>
       <c r="F6" s="20" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="G6" s="24"/>
     </row>
@@ -2414,19 +2614,19 @@
         <v>725</v>
       </c>
       <c r="B7" s="21" t="s">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="C7" s="21" t="s">
         <v>13</v>
       </c>
       <c r="D7" s="22" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="E7" s="21" t="n">
         <v>35</v>
       </c>
       <c r="F7" s="20" t="s">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="G7" s="24"/>
     </row>
@@ -2435,13 +2635,13 @@
         <v>25</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>146</v>
+        <v>151</v>
       </c>
       <c r="C8" s="25" t="s">
         <v>23</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="E8" s="25" t="n">
         <v>36</v>
@@ -2454,24 +2654,24 @@
         <v>2074</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>148</v>
+        <v>153</v>
       </c>
       <c r="C9" s="25" t="s">
-        <v>149</v>
+        <v>154</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="E9" s="25" t="n">
         <v>37</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>151</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="52.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="D20" s="19" t="s">
-        <v>152</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2529,7 +2729,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="30" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="F1" s="30" t="s">
         <v>5</v>
@@ -2540,19 +2740,19 @@
         <v>2231</v>
       </c>
       <c r="B2" s="19" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
       <c r="E2" s="19" t="n">
         <v>41</v>
       </c>
       <c r="F2" s="19" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2560,19 +2760,19 @@
         <v>295</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="C3" s="19" t="s">
         <v>23</v>
       </c>
       <c r="D3" s="19" t="s">
-        <v>157</v>
+        <v>162</v>
       </c>
       <c r="E3" s="19" t="n">
         <v>42</v>
       </c>
       <c r="F3" s="19" t="s">
-        <v>158</v>
+        <v>163</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2580,19 +2780,19 @@
         <v>1942</v>
       </c>
       <c r="B4" s="19" t="s">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="C4" s="19" t="s">
         <v>13</v>
       </c>
       <c r="D4" s="19" t="s">
-        <v>160</v>
+        <v>165</v>
       </c>
       <c r="E4" s="19" t="n">
         <v>43</v>
       </c>
       <c r="F4" s="19" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2600,19 +2800,19 @@
         <v>2402</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="C5" s="19" t="s">
         <v>23</v>
       </c>
       <c r="D5" s="19" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="E5" s="19" t="n">
         <v>44</v>
       </c>
       <c r="F5" s="19" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -2630,4 +2830,184 @@
     <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="16.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="64.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="84.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="51.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="68.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="50.08"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="8" style="1" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="6" width="11.53"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="31" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="31" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="31" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="6" t="n">
+        <v>104</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="F2" s="32" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="6" t="n">
+        <v>110</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="F3" s="32"/>
+    </row>
+    <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6"/>
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+    </row>
+    <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>543</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="F5" s="32" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>124</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="F6" s="32"/>
+    </row>
+    <row r="7" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>563</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>687</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="33" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="F5:F6"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/maximum-depth-of-binary-tree/"/>
+    <hyperlink ref="E2" r:id="rId2" display="https://youtu.be/eD3tmO66aBA"/>
+    <hyperlink ref="D3" r:id="rId3" display="https://leetcode.com/problems/balanced-binary-tree/"/>
+    <hyperlink ref="E3" r:id="rId4" display="https://youtu.be/Yt50Jfbd8Po"/>
+    <hyperlink ref="D5" r:id="rId5" display="https://leetcode.com/problems/diameter-of-binary-tree/"/>
+    <hyperlink ref="E5" r:id="rId6" display="https://youtu.be/Rezetez59Nk"/>
+    <hyperlink ref="D6" r:id="rId7" display="https://leetcode.com/problems/binary-tree-maximum-path-sum/"/>
+    <hyperlink ref="E6" r:id="rId8" display="https://youtu.be/WszrfSwMz58"/>
+    <hyperlink ref="D7" r:id="rId9" display="https://leetcode.com/problems/binary-tree-tilt/"/>
+    <hyperlink ref="D8" r:id="rId10" display="https://leetcode.com/problems/longest-univalue-path/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
 </file>
--- a/3.Problems for Revision.xlsx
+++ b/3.Problems for Revision.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="8"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Practice Problems (Striver + Ku" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="211">
   <si>
     <t xml:space="preserve">No.</t>
   </si>
@@ -47,6 +47,78 @@
   </si>
   <si>
     <t xml:space="preserve">NOTES</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Beginner Questions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Two Sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/two-sum</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roman To Integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/roman-to-integer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palindrome Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/palindrome-number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum Subarray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/maximum-subarray</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove Elelment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/remove-element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contains Duplicate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/contains-duplicate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Add Two Numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/add-two-numbers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Majority Element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/majority-element</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Remove Duplicates from Sorted Array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/remove-duplicates-from-sorted-array</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valid Anagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/valid-anagram</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Group Anagrams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://leetcode.com/problems/group-anagrams</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intermediate + Hard Questions</t>
   </si>
   <si>
     <t xml:space="preserve">Pascal’s Triangle</t>
@@ -599,7 +671,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,13 +696,6 @@
     </font>
     <font>
       <sz val="13"/>
-      <color theme="1"/>
-      <name val="Comic Sans MS"/>
-      <family val="4"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
       <name val="Comic Sans MS"/>
       <family val="4"/>
@@ -801,11 +866,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="38">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -814,16 +879,36 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -838,7 +923,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -846,11 +931,11 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -862,7 +947,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -870,19 +959,19 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -890,27 +979,23 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -922,24 +1007,20 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1192,198 +1273,423 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F1048576"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15.85" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="52.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="13.36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="69.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="70.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="31.39"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="2" width="13.54"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="2" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="51.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="88.26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="44.98"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="34.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="13.54"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="8" style="1" width="11.53"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+    <row r="1" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
+    <row r="2" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="4"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+    </row>
+    <row r="3" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="4"/>
+      <c r="B3" s="4"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+    </row>
+    <row r="4" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4"/>
+      <c r="D4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+    </row>
+    <row r="5" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="6"/>
+      <c r="D5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+    </row>
+    <row r="6" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="6"/>
+      <c r="D6" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+    </row>
+    <row r="7" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C7" s="6"/>
+      <c r="D7" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+    </row>
+    <row r="8" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="6"/>
+      <c r="D8" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="8"/>
+      <c r="F8" s="8"/>
+    </row>
+    <row r="9" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="n">
+        <v>217</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C9" s="6"/>
+      <c r="D9" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="8"/>
+      <c r="F9" s="8"/>
+    </row>
+    <row r="10" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="C10" s="6"/>
+      <c r="D10" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="n">
+        <v>169</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="n">
+        <v>242</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="6"/>
+      <c r="D13" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="n">
+        <v>49</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C14" s="6"/>
+      <c r="D14" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="4"/>
+      <c r="B15" s="4"/>
+      <c r="C15" s="4"/>
+      <c r="D15" s="4"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="16" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="4"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="4"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+    </row>
+    <row r="17" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="4"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="4"/>
+      <c r="D17" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+    </row>
+    <row r="18" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="4"/>
+      <c r="B18" s="4"/>
+      <c r="C18" s="4"/>
+      <c r="D18" s="4"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+    </row>
+    <row r="19" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="n">
         <v>118</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="1" t="n">
+      <c r="B19" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="1" t="n">
         <v>119</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="1" t="n">
+      <c r="B20" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+    </row>
+    <row r="22" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="1" t="n">
         <v>15</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="n">
+      <c r="B22" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="n">
         <v>16</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="1" t="s">
+      <c r="B23" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="n">
         <v>17</v>
       </c>
-      <c r="E5" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="1" t="n">
-        <v>17</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="1" t="n">
+      <c r="B24" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="F24" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="1" t="n">
-        <v>37</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="1" t="n">
+      <c r="B25" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="n">
         <v>36</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B27" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="F27" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://leetcode.com/problems/pascals-triangle/"/>
-    <hyperlink ref="E2" r:id="rId2" display="https://youtu.be/ELo7RR-Isjk"/>
-    <hyperlink ref="D3" r:id="rId3" display="https://leetcode.com/problems/pascals-triangle-ii/"/>
-    <hyperlink ref="D4" r:id="rId4" display="https://leetcode.com/problems/3sum/"/>
-    <hyperlink ref="E4" r:id="rId5" display="https://youtu.be/rM9EthMlXnw"/>
-    <hyperlink ref="D5" r:id="rId6" display="https://leetcode.com/problems/3sum-closest/"/>
-    <hyperlink ref="E5" r:id="rId7" display="https://youtu.be/rM9EthMlXnw"/>
-    <hyperlink ref="D6" r:id="rId8" display="https://leetcode.com/problems/letter-combinations-of-a-phone-number/"/>
-    <hyperlink ref="E6" r:id="rId9" display="https://youtu.be/9ByWqPzfXDU"/>
-    <hyperlink ref="D7" r:id="rId10" display="https://leetcode.com/problems/n-queens/"/>
-    <hyperlink ref="E7" r:id="rId11" display="https://youtu.be/nC1rbW2YSz0"/>
-    <hyperlink ref="D8" r:id="rId12" display="https://leetcode.com/problems/sudoku-solver/"/>
-    <hyperlink ref="E8" r:id="rId13" display="https://youtu.be/nC1rbW2YSz0"/>
-    <hyperlink ref="D9" r:id="rId14" display="https://leetcode.com/problems/valid-sudoku/"/>
+    <hyperlink ref="D4" r:id="rId1" display="https://leetcode.com/problems/two-sum"/>
+    <hyperlink ref="D5" r:id="rId2" display="https://leetcode.com/problems/roman-to-integer"/>
+    <hyperlink ref="D6" r:id="rId3" display="https://leetcode.com/problems/palindrome-number"/>
+    <hyperlink ref="D7" r:id="rId4" display="https://leetcode.com/problems/maximum-subarray"/>
+    <hyperlink ref="D8" r:id="rId5" display="https://leetcode.com/problems/remove-element"/>
+    <hyperlink ref="D9" r:id="rId6" display="https://leetcode.com/problems/contains-duplicate"/>
+    <hyperlink ref="D10" r:id="rId7" display="https://leetcode.com/problems/add-two-numbers"/>
+    <hyperlink ref="D11" r:id="rId8" display="https://leetcode.com/problems/majority-element"/>
+    <hyperlink ref="D12" r:id="rId9" display="https://leetcode.com/problems/remove-duplicates-from-sorted-array"/>
+    <hyperlink ref="D13" r:id="rId10" display="https://leetcode.com/problems/valid-anagram"/>
+    <hyperlink ref="D14" r:id="rId11" display="https://leetcode.com/problems/group-anagrams"/>
+    <hyperlink ref="D19" r:id="rId12" display="https://leetcode.com/problems/pascals-triangle/"/>
+    <hyperlink ref="E19" r:id="rId13" display="https://youtu.be/ELo7RR-Isjk"/>
+    <hyperlink ref="D20" r:id="rId14" display="https://leetcode.com/problems/pascals-triangle-ii/"/>
+    <hyperlink ref="D22" r:id="rId15" display="https://leetcode.com/problems/3sum/"/>
+    <hyperlink ref="E22" r:id="rId16" display="https://youtu.be/rM9EthMlXnw"/>
+    <hyperlink ref="D23" r:id="rId17" display="https://leetcode.com/problems/3sum-closest/"/>
+    <hyperlink ref="E23" r:id="rId18" display="https://youtu.be/rM9EthMlXnw"/>
+    <hyperlink ref="D24" r:id="rId19" display="https://leetcode.com/problems/letter-combinations-of-a-phone-number/"/>
+    <hyperlink ref="E24" r:id="rId20" display="https://youtu.be/9ByWqPzfXDU"/>
+    <hyperlink ref="D25" r:id="rId21" display="https://leetcode.com/problems/n-queens/"/>
+    <hyperlink ref="E25" r:id="rId22" display="https://youtu.be/nC1rbW2YSz0"/>
+    <hyperlink ref="D26" r:id="rId23" display="https://leetcode.com/problems/sudoku-solver/"/>
+    <hyperlink ref="E26" r:id="rId24" display="https://youtu.be/nC1rbW2YSz0"/>
+    <hyperlink ref="D27" r:id="rId25" display="https://leetcode.com/problems/valid-sudoku/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1403,76 +1709,76 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="64.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="19.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="69.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="51.01"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="68.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="19" width="50.08"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="19" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="23" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="24" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="24" width="64.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="24" width="19.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="24" width="69.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="24" width="51.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="24" width="68.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="24" width="50.08"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="24" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="28" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="13"/>
-      <c r="B2" s="13"/>
-      <c r="C2" s="13"/>
-      <c r="D2" s="13"/>
-      <c r="E2" s="13"/>
-      <c r="F2" s="13"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="13"/>
-      <c r="B3" s="13"/>
-      <c r="C3" s="13"/>
-      <c r="D3" s="13"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
+      <c r="F4" s="18"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13"/>
-      <c r="B5" s="13"/>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -1504,22 +1810,22 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
@@ -1528,19 +1834,19 @@
         <v>34</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>35</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1548,19 +1854,19 @@
         <v>875</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>39</v>
+        <v>62</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1568,73 +1874,73 @@
         <v>1482</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>64</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F5" s="5"/>
+        <v>66</v>
+      </c>
+      <c r="F5" s="10"/>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
         <v>1011</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="F6" s="5"/>
+        <v>69</v>
+      </c>
+      <c r="F6" s="10"/>
     </row>
     <row r="7" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
         <v>410</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F7" s="5"/>
+        <v>71</v>
+      </c>
+      <c r="F7" s="10"/>
     </row>
     <row r="8" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F8" s="5"/>
+      <c r="F8" s="10"/>
     </row>
     <row r="10" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
         <v>33</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>48</v>
+        <v>72</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>51</v>
+        <v>74</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1642,18 +1948,18 @@
         <v>81</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>53</v>
+        <v>77</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="5"/>
+        <v>78</v>
+      </c>
+      <c r="F11" s="10"/>
     </row>
     <row r="12" customFormat="false" ht="15.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="13" customFormat="false" ht="19.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1661,16 +1967,16 @@
         <v>2305</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>55</v>
+        <v>79</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>13</v>
+        <v>37</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>57</v>
+        <v>80</v>
+      </c>
+      <c r="F13" s="10" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1678,32 +1984,32 @@
         <v>1723</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>82</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="5"/>
-    </row>
-    <row r="16" s="6" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
+        <v>83</v>
+      </c>
+      <c r="F14" s="10"/>
+    </row>
+    <row r="15" s="11" customFormat="true" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
     </row>
     <row r="19" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="6"/>
-      <c r="B19" s="6"/>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="11"/>
+      <c r="E19" s="11"/>
+      <c r="F19" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -1746,148 +2052,148 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr defaultColWidth="129.5625" defaultRowHeight="19.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="69.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="85.96"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="129.33"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="7" width="129.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="69.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="85.96"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="129.33"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="12" width="129.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>60</v>
+      <c r="E1" s="13" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="12" t="n">
         <v>410</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="C2" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" s="10" t="s">
-        <v>61</v>
-      </c>
-      <c r="E2" s="10" t="s">
-        <v>62</v>
+      <c r="B2" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C2" s="14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="E2" s="15" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
+      <c r="A3" s="12" t="n">
         <v>1365</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>64</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>65</v>
+      <c r="B3" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>68</v>
+      <c r="B4" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="15" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="12" t="n">
         <v>1650</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>68</v>
+      <c r="B5" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="12" t="n">
         <v>151</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="E6" s="10" t="s">
-        <v>73</v>
+      <c r="B6" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>96</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="12" t="n">
         <v>557</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>74</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>65</v>
+      <c r="B7" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="15" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="19.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="12" t="n">
         <v>1886</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>65</v>
+      <c r="B8" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="15" t="s">
+        <v>101</v>
+      </c>
+      <c r="E8" s="12" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>
@@ -1922,96 +2228,96 @@
   <dimension ref="A1:E5"/>
   <sheetFormatPr defaultColWidth="129.5625" defaultRowHeight="19.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="6.67"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="69.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="9.88"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="87.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="11.44"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="7" width="129.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="6.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="69.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="9.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="87.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="11.44"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="6" style="12" width="129.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>78</v>
+      <c r="E1" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="11" t="n">
+      <c r="A2" s="16" t="n">
         <v>142</v>
       </c>
-      <c r="B2" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E2" s="7" t="n">
+      <c r="B2" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E2" s="12" t="n">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="n">
+      <c r="A3" s="16" t="n">
         <v>287</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>82</v>
-      </c>
-      <c r="E3" s="7" t="n">
+      <c r="B3" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E3" s="12" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="12" t="n">
         <v>234</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="7" t="n">
+      <c r="B4" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="E4" s="12" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="12" t="n">
         <v>457</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="7" t="n">
+      <c r="B5" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>11</v>
       </c>
     </row>
@@ -2034,208 +2340,208 @@
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="19.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="7" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="7" width="63.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="7" width="12.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="7" width="67.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="7" width="13.6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="7" width="43.9"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="7" width="8.88"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="12" width="7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="63.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="12" width="12.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="67.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="12" width="13.6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="43.9"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="12" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>87</v>
+      <c r="E1" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="7" t="n">
+      <c r="A2" s="12" t="n">
         <v>209</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="C2" s="7" t="s">
+      <c r="B2" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="12" t="s">
+        <v>113</v>
+      </c>
+      <c r="E2" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="D2" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E2" s="7" t="n">
+    </row>
+    <row r="3" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="12" t="n">
+        <v>2461</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>114</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="E3" s="12" t="n">
         <v>13</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="7" t="n">
-        <v>2461</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E3" s="7" t="n">
-        <v>13</v>
-      </c>
-    </row>
     <row r="4" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7" t="n">
+      <c r="A4" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="E4" s="7" t="n">
+      <c r="B4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="E4" s="12" t="n">
         <v>14</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="12" t="n">
         <v>187</v>
       </c>
-      <c r="B5" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="7" t="n">
+      <c r="B5" s="12" t="s">
+        <v>118</v>
+      </c>
+      <c r="C5" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="E5" s="12" t="n">
         <v>15</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="12" t="n">
         <v>904</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="E6" s="7" t="n">
+      <c r="B6" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="12" t="s">
+        <v>121</v>
+      </c>
+      <c r="E6" s="12" t="n">
         <v>16</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="39.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="12" t="n">
         <v>1838</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="7" t="n">
+      <c r="B7" s="12" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="F7" s="12" t="s">
-        <v>100</v>
+      <c r="F7" s="17" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="12" t="n">
         <v>424</v>
       </c>
-      <c r="B8" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="7" t="n">
+      <c r="B8" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D8" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F8" s="12" t="s">
-        <v>103</v>
+      <c r="F8" s="17" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="12" t="n">
         <v>1493</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>107</v>
+      <c r="B9" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="12" t="n">
         <v>1004</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>103</v>
+      <c r="B10" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="C10" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>133</v>
+      </c>
+      <c r="E10" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="19.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13"/>
-      <c r="B11" s="13"/>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
-      <c r="G11" s="14"/>
+      <c r="A11" s="18"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2260,190 +2566,190 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="15" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="15" width="35.2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="15" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="15" width="68.45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="15" width="18.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="15" width="59.26"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="15" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="20" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="20" width="35.2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="20" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="20" width="68.45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="20" width="18.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="20" width="59.26"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="20" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>87</v>
+      <c r="E1" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="15" t="n">
+      <c r="A2" s="20" t="n">
         <v>56</v>
       </c>
-      <c r="B2" s="15" t="s">
-        <v>110</v>
-      </c>
-      <c r="C2" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D2" s="15" t="s">
-        <v>112</v>
-      </c>
-      <c r="E2" s="15" t="n">
+      <c r="B2" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C2" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="20" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="20" t="n">
         <v>21</v>
       </c>
-      <c r="F2" s="15" t="s">
-        <v>113</v>
+      <c r="F2" s="20" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="15" t="n">
+      <c r="A3" s="20" t="n">
         <v>986</v>
       </c>
-      <c r="B3" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>111</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="E3" s="15" t="n">
+      <c r="B3" s="20" t="s">
+        <v>138</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>135</v>
+      </c>
+      <c r="D3" s="20" t="s">
+        <v>139</v>
+      </c>
+      <c r="E3" s="20" t="n">
         <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="16" t="n">
+      <c r="A4" s="21" t="n">
         <v>57</v>
       </c>
-      <c r="B4" s="17" t="s">
-        <v>116</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E4" s="17" t="n">
+      <c r="B4" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="C4" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="23" t="s">
+        <v>141</v>
+      </c>
+      <c r="E4" s="22" t="n">
         <v>23</v>
       </c>
-      <c r="F4" s="16" t="s">
-        <v>118</v>
+      <c r="F4" s="21" t="s">
+        <v>142</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="15" t="n">
+      <c r="A5" s="20" t="n">
         <v>1288</v>
       </c>
-      <c r="B5" s="15" t="s">
-        <v>119</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="15" t="s">
-        <v>120</v>
-      </c>
-      <c r="E5" s="15" t="n">
+      <c r="B5" s="20" t="s">
+        <v>143</v>
+      </c>
+      <c r="C5" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="20" t="s">
+        <v>144</v>
+      </c>
+      <c r="E5" s="20" t="n">
         <v>24</v>
       </c>
-      <c r="F5" s="15" t="s">
-        <v>121</v>
+      <c r="F5" s="20" t="s">
+        <v>145</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="20" t="n">
         <v>731</v>
       </c>
-      <c r="B6" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="15" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="15" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="15" t="s">
-        <v>125</v>
+      <c r="B6" s="20" t="s">
+        <v>146</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="20" t="s">
+        <v>147</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>148</v>
+      </c>
+      <c r="F6" s="20" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="20" t="n">
         <v>729</v>
       </c>
-      <c r="B7" s="15" t="s">
-        <v>126</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>127</v>
-      </c>
-      <c r="E7" s="15" t="n">
+      <c r="B7" s="20" t="s">
+        <v>150</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>151</v>
+      </c>
+      <c r="E7" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="F7" s="15" t="s">
-        <v>125</v>
+      <c r="F7" s="20" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="20" t="n">
         <v>732</v>
       </c>
-      <c r="B8" s="15" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>129</v>
-      </c>
-      <c r="E8" s="15" t="n">
+      <c r="B8" s="20" t="s">
+        <v>152</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>153</v>
+      </c>
+      <c r="E8" s="20" t="n">
         <v>29</v>
       </c>
-      <c r="F8" s="15" t="s">
-        <v>125</v>
+      <c r="F8" s="20" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="18.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="20" t="n">
         <v>352</v>
       </c>
-      <c r="B9" s="15" t="s">
-        <v>130</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="15" t="n">
+      <c r="B9" s="20" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="F9" s="15" t="s">
-        <v>132</v>
+      <c r="F9" s="20" t="s">
+        <v>156</v>
       </c>
     </row>
   </sheetData>
@@ -2475,203 +2781,203 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="16.15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="8.05"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="37.87"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="23.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="72.65"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="11.53"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="48.38"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="19" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="24" width="8.05"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="24" width="37.87"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="24" width="23.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="24" width="72.65"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="5" min="5" style="24" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="24" width="48.38"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="7" style="24" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="B1" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="C1" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="D1" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>87</v>
+      <c r="E1" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="13" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="20" t="n">
+      <c r="A2" s="25" t="n">
         <v>206</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="22" t="s">
-        <v>134</v>
-      </c>
-      <c r="E2" s="21" t="n">
+      <c r="B2" s="26" t="s">
+        <v>157</v>
+      </c>
+      <c r="C2" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" s="26" t="n">
         <v>32</v>
       </c>
-      <c r="F2" s="20" t="s">
-        <v>135</v>
-      </c>
-      <c r="G2" s="23"/>
+      <c r="F2" s="25" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="28"/>
     </row>
     <row r="3" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="20" t="n">
+      <c r="A3" s="25" t="n">
         <v>203</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>136</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="22" t="s">
-        <v>137</v>
-      </c>
-      <c r="E3" s="21" t="n">
+      <c r="B3" s="26" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="27" t="s">
+        <v>161</v>
+      </c>
+      <c r="E3" s="26" t="n">
         <v>32</v>
       </c>
-      <c r="F3" s="20" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="23"/>
+      <c r="F3" s="25" t="s">
+        <v>162</v>
+      </c>
+      <c r="G3" s="28"/>
     </row>
     <row r="4" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="20" t="n">
+      <c r="A4" s="25" t="n">
         <v>92</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="E4" s="21" t="n">
+      <c r="B4" s="26" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="E4" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="F4" s="20" t="s">
-        <v>141</v>
-      </c>
-      <c r="G4" s="23"/>
+      <c r="F4" s="25" t="s">
+        <v>165</v>
+      </c>
+      <c r="G4" s="28"/>
     </row>
     <row r="5" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="n">
+      <c r="A5" s="25" t="n">
         <v>143</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>142</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="22" t="s">
-        <v>143</v>
-      </c>
-      <c r="E5" s="21" t="n">
+      <c r="B5" s="26" t="s">
+        <v>166</v>
+      </c>
+      <c r="C5" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D5" s="27" t="s">
+        <v>167</v>
+      </c>
+      <c r="E5" s="26" t="n">
         <v>33</v>
       </c>
-      <c r="F5" s="20" t="s">
-        <v>144</v>
-      </c>
-      <c r="G5" s="23"/>
+      <c r="F5" s="25" t="s">
+        <v>168</v>
+      </c>
+      <c r="G5" s="28"/>
     </row>
     <row r="6" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="25" t="n">
         <v>328</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="C6" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="22" t="s">
-        <v>146</v>
-      </c>
-      <c r="E6" s="21" t="n">
+      <c r="B6" s="26" t="s">
+        <v>169</v>
+      </c>
+      <c r="C6" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="27" t="s">
+        <v>170</v>
+      </c>
+      <c r="E6" s="26" t="n">
         <v>34</v>
       </c>
-      <c r="F6" s="20" t="s">
-        <v>147</v>
-      </c>
-      <c r="G6" s="24"/>
+      <c r="F6" s="25" t="s">
+        <v>171</v>
+      </c>
+      <c r="G6" s="29"/>
     </row>
     <row r="7" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="n">
+      <c r="A7" s="25" t="n">
         <v>725</v>
       </c>
-      <c r="B7" s="21" t="s">
-        <v>148</v>
-      </c>
-      <c r="C7" s="21" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E7" s="21" t="n">
+      <c r="B7" s="26" t="s">
+        <v>172</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>37</v>
+      </c>
+      <c r="D7" s="27" t="s">
+        <v>173</v>
+      </c>
+      <c r="E7" s="26" t="n">
         <v>35</v>
       </c>
-      <c r="F7" s="20" t="s">
-        <v>150</v>
-      </c>
-      <c r="G7" s="24"/>
+      <c r="F7" s="25" t="s">
+        <v>174</v>
+      </c>
+      <c r="G7" s="29"/>
     </row>
     <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="24" t="n">
         <v>25</v>
       </c>
-      <c r="B8" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>23</v>
-      </c>
-      <c r="D8" s="26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E8" s="25" t="n">
+      <c r="B8" s="30" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="D8" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="E8" s="30" t="n">
         <v>36</v>
       </c>
-      <c r="F8" s="27"/>
-      <c r="G8" s="28"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="33"/>
     </row>
     <row r="9" customFormat="false" ht="37.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="12" t="n">
         <v>2074</v>
       </c>
-      <c r="B9" s="25" t="s">
-        <v>153</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>155</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>37</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>156</v>
+      <c r="B9" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="C9" s="30" t="s">
+        <v>178</v>
+      </c>
+      <c r="D9" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>37</v>
+      </c>
+      <c r="F9" s="32" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="52.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="D20" s="19" t="s">
-        <v>157</v>
+      <c r="D20" s="24" t="s">
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -2703,116 +3009,116 @@
   <dimension ref="A1:F5"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="19" width="8.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="19" width="64.07"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="19" width="19.77"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="19" width="69.19"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="19" width="10.4"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="19" width="68.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="19" width="50.08"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="19" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="23" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="19" width="11.53"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="24" width="8.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="24" width="64.07"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="24" width="19.77"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="24" width="69.19"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="24" width="10.4"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="24" width="68.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="24" width="50.08"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16382" min="8" style="24" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="16383" style="28" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="24" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="29" t="s">
+      <c r="A1" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="29" t="s">
+      <c r="B1" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29" t="s">
+      <c r="C1" s="34" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="29" t="s">
+      <c r="D1" s="34" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="30" t="s">
-        <v>78</v>
-      </c>
-      <c r="F1" s="30" t="s">
+      <c r="E1" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="35" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="19" t="n">
+      <c r="A2" s="24" t="n">
         <v>2231</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>158</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>159</v>
-      </c>
-      <c r="E2" s="19" t="n">
+      <c r="B2" s="24" t="s">
+        <v>182</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>183</v>
+      </c>
+      <c r="E2" s="24" t="n">
         <v>41</v>
       </c>
-      <c r="F2" s="19" t="s">
-        <v>160</v>
+      <c r="F2" s="24" t="s">
+        <v>184</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="19" t="n">
+      <c r="A3" s="24" t="n">
         <v>295</v>
       </c>
-      <c r="B3" s="19" t="s">
-        <v>161</v>
-      </c>
-      <c r="C3" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="19" t="s">
-        <v>162</v>
-      </c>
-      <c r="E3" s="19" t="n">
+      <c r="B3" s="24" t="s">
+        <v>185</v>
+      </c>
+      <c r="C3" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D3" s="24" t="s">
+        <v>186</v>
+      </c>
+      <c r="E3" s="24" t="n">
         <v>42</v>
       </c>
-      <c r="F3" s="19" t="s">
-        <v>163</v>
+      <c r="F3" s="24" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="19" t="n">
+      <c r="A4" s="24" t="n">
         <v>1942</v>
       </c>
-      <c r="B4" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C4" s="19" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="E4" s="19" t="n">
+      <c r="B4" s="24" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="24" t="s">
+        <v>189</v>
+      </c>
+      <c r="E4" s="24" t="n">
         <v>43</v>
       </c>
-      <c r="F4" s="19" t="s">
-        <v>166</v>
+      <c r="F4" s="24" t="s">
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="18.65" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="n">
+      <c r="A5" s="24" t="n">
         <v>2402</v>
       </c>
-      <c r="B5" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="C5" s="19" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="E5" s="19" t="n">
+      <c r="B5" s="24" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="24" t="n">
         <v>44</v>
       </c>
-      <c r="F5" s="19" t="s">
-        <v>169</v>
+      <c r="F5" s="24" t="s">
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2848,141 +3154,141 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="68.72"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="50.08"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16383" min="8" style="1" width="11.53"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="6" width="11.53"/>
+    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="16384" style="11" width="11.53"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="31" t="s">
+      <c r="B1" s="36" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="31" t="s">
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="31" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="6" t="n">
+      <c r="A2" s="11" t="n">
         <v>104</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="F2" s="32" t="s">
-        <v>173</v>
+      <c r="B2" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="37" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="11" t="n">
         <v>110</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>174</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>175</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>176</v>
-      </c>
-      <c r="F3" s="32"/>
+      <c r="B3" s="11" t="s">
+        <v>198</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="E3" s="11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F3" s="37"/>
     </row>
     <row r="4" customFormat="false" ht="16.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="6"/>
-      <c r="B4" s="6"/>
-      <c r="C4" s="6"/>
-      <c r="D4" s="6"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="11"/>
     </row>
     <row r="5" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="11" t="n">
         <v>543</v>
       </c>
-      <c r="B5" s="6" t="s">
-        <v>177</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>178</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>179</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>173</v>
+      <c r="B5" s="11" t="s">
+        <v>201</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" s="37" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="11" t="n">
         <v>124</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>181</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="F6" s="32"/>
-    </row>
-    <row r="7" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+      <c r="B6" s="11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>206</v>
+      </c>
+      <c r="F6" s="37"/>
+    </row>
+    <row r="7" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="11" t="n">
         <v>563</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>183</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>184</v>
-      </c>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-    </row>
-    <row r="8" customFormat="false" ht="20.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="11" t="s">
+        <v>207</v>
+      </c>
+      <c r="C7" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+    </row>
+    <row r="8" customFormat="false" ht="19.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
         <v>687</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>185</v>
+        <v>209</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="33" t="s">
-        <v>186</v>
+        <v>37</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
